--- a/video_gen_eval/templates/pe_eval.xlsx
+++ b/video_gen_eval/templates/pe_eval.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Evaluation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,85 +607,90 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ground_truth / criteria</t>
+          <t>ground_truth</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>error_examples</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>veo31_video</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>veo31_score</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>veo31_notes</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>sora2_video</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>sora2_score</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>sora2_notes</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>kling3_video</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>kling3_score</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>kling3_notes</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>wan22_video</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>wan22_score</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>wan22_notes</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>wan26_video</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>wan26_score</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>wan26_notes</t>
         </is>
@@ -730,46 +735,51 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
+          <t>- The video must accurately depict a rectangular basketball court measuring 28 meters in length and 15 meters in width, including a center circle, three-point line at 6.75 meters from the basket, free throw line at 4.6 meters from the backboard, and the key (painted area), with each marking clearly labeled.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
           <t>- Wrong dimensions
 - Missing three-point line
 - Incorrect free throw distance</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>073_veo31_EVB-Art-Mid-K-CK-F-093.mp4</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>073_sora2_EVB-Art-Mid-K-CK-F-093.mp4</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="12" t="inlineStr">
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="8" t="n"/>
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>073_kling3_EVB-Art-Mid-K-CK-F-093.mp4</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="13" t="inlineStr">
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="8" t="n"/>
+      <c r="S2" s="13" t="inlineStr">
         <is>
           <t>073_wan22_EVB-Art-Mid-K-CK-F-093.mp4</t>
         </is>
       </c>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="14" t="inlineStr">
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="8" t="n"/>
+      <c r="V2" s="14" t="inlineStr">
         <is>
           <t>073_wan26_EVB-Art-Mid-K-CK-F-093.mp4</t>
         </is>
       </c>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="8" t="inlineStr"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="8" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -810,46 +820,51 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
+          <t>- The video must visually demonstrate each phase of the warm-up routine: light cardio (jogging in place), dynamic stretching (arm circles, leg swings, torso twists), and sport-specific movements.</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
           <t>- Starting with static stretching
 - Skipping cardio phase
 - Wrong order</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>074_veo31_EVB-Art-High-K-CK-P-094.mp4</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>074_sora2_EVB-Art-High-K-CK-P-094.mp4</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>074_kling3_EVB-Art-High-K-CK-P-094.mp4</t>
         </is>
       </c>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t>074_wan22_EVB-Art-High-K-CK-P-094.mp4</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="14" t="inlineStr">
         <is>
           <t>074_wan26_EVB-Art-High-K-CK-P-094.mp4</t>
         </is>
       </c>
-      <c r="V3" s="10" t="inlineStr"/>
-      <c r="W3" s="8" t="inlineStr"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="8" t="n"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -874,7 +889,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -885,46 +900,61 @@
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Answer: Proper forward roll technique with correct body mechanics and safety positions
-Key visuals: squat start position, hands flat on mat, chin tucked to chest, rolling along curved spine, landing in squat
-Rubric: 9-10: All four phases shown clearly with correct body mechanics, close-ups of hand placement and chin tuck for safety, smooth and natural movement. 7-8: Most phases correct with minor inaccuracies in body position, safety elements mostly present. 5-6: Basic forward roll shown but missing some phases or safety details, some body mechanics incorrect. 3-4: Attempt at forward roll but significant errors in technique, missing safety elements. 1-2: No recognizable forward roll or completely incorrect movement.</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr">
+Key visuals: squat start position, hands flat on mat, chin tucked to chest, rolling along curved spine, landing in squat</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>- 5: All four phases shown clearly with correct body mechanics, close-ups of hand placement and chin tuck for safety, smooth and natural movement
+- 4: Most phases correct with minor inaccuracies in body position, safety elements mostly present
+- 3: Basic forward roll shown but missing some phases or safety details, some body mechanics incorrect
+- 2: Attempt at forward roll but significant errors in technique, missing safety elements
+- 1: No recognizable forward roll or completely incorrect movement</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>- Incorrect hand placement during the squat position, leading to potential safety issues.
+- Failing to tuck the chin to the chest, resulting in an unsafe roll.
+- Rolling flat instead of along the curved spine, which can cause injury.
+- Not demonstrating a proper landing back in the squat position.</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>071_veo31_EVB-Art-EHigh-S-PF-D-093.mp4</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>071_sora2_EVB-Art-EHigh-S-PF-D-093.mp4</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="8" t="n"/>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>071_kling3_EVB-Art-EHigh-S-PF-D-093.mp4</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="8" t="n"/>
+      <c r="S4" s="13" t="inlineStr">
         <is>
           <t>071_wan22_EVB-Art-EHigh-S-PF-D-093.mp4</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="14" t="inlineStr">
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="8" t="n"/>
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>071_wan26_EVB-Art-EHigh-S-PF-D-093.mp4</t>
         </is>
       </c>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="8" t="inlineStr"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="8" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -949,7 +979,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -960,46 +990,61 @@
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Answer: Anatomical visualization of muscle activation during squat: quadriceps, hamstrings, glutes, and core with color-coded phases
-Key visuals: person performing squat, anatomical overlay, quadriceps highlighted, hamstrings highlighted, glutes highlighted, core muscles
-Rubric: 9-10: Clear anatomical overlay with all four muscle groups correctly identified and color-coded, accurate activation timing during downward/upward phases. 7-8: Most muscle groups shown correctly with some color coding, minor inaccuracies in activation timing. 5-6: Some muscles identified but overlay is unclear or some groups missing, limited phase distinction. 3-4: Attempt at muscle visualization but mostly inaccurate muscle locations or missing key groups. 1-2: No recognizable anatomical overlay or completely wrong muscle identification.</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr">
+Key visuals: person performing squat, anatomical overlay, quadriceps highlighted, hamstrings highlighted, glutes highlighted, core muscles</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Clear anatomical overlay with all four muscle groups correctly identified and color-coded, accurate activation timing during downward/upward phases
+- 4: Most muscle groups shown correctly with some color coding, minor inaccuracies in activation timing
+- 3: Some muscles identified but overlay is unclear or some groups missing, limited phase distinction
+- 2: Attempt at muscle visualization but mostly inaccurate muscle locations or missing key groups
+- 1: No recognizable anatomical overlay or completely wrong muscle identification</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>- Missing the anatomical overlay entirely, showing only a person performing a squat
+- Incorrectly highlighting the wrong muscle groups, such as the calves instead of the hamstrings
+- Using the wrong colors for muscle activation, leading to confusion in identification
+- Failing to show the activation timing during the squat phases, making it unclear when each muscle is engaged</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>072_veo31_EVB-Art-Mid-S-PF-V-094.mp4</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>072_sora2_EVB-Art-Mid-S-PF-V-094.mp4</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="8" t="n"/>
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>072_kling3_EVB-Art-Mid-S-PF-V-094.mp4</t>
         </is>
       </c>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>072_wan22_EVB-Art-Mid-S-PF-V-094.mp4</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="14" t="inlineStr">
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>072_wan26_EVB-Art-Mid-S-PF-V-094.mp4</t>
         </is>
       </c>
-      <c r="V5" s="10" t="inlineStr"/>
-      <c r="W5" s="8" t="inlineStr"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="8" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1024,7 +1069,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1035,46 +1080,61 @@
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Answer: Simple animated explanation of basic soccer rules suitable for young children
-Key visuals: colorful animated characters, kid-friendly soccer field, ball being kicked into goal, goalkeeper using hands, scoreboard
-Rubric: 9-10: All three basic rules clearly explained with age-appropriate animation, colorful characters, engaging and easy to follow for young children. 7-8: Most rules covered with appealing animation, minor clarity issues but generally appropriate for young learners. 5-6: Some rules presented but animation is not fully age-appropriate or some rules unclear. 3-4: Attempt at soccer rules but confusing for young children, missing key rules or overly complex. 1-2: No recognizable soccer rules or completely inappropriate for the age group.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
+Key visuals: colorful animated characters, kid-friendly soccer field, ball being kicked into goal, goalkeeper using hands, scoreboard</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>- 5: All three basic rules clearly explained with age-appropriate animation, colorful characters, engaging and easy to follow for young children
+- 4: Most rules covered with appealing animation, minor clarity issues but generally appropriate for young learners
+- 3: Some rules presented but animation is not fully age-appropriate or some rules unclear
+- 2: Attempt at soccer rules but confusing for young children, missing key rules or overly complex
+- 1: No recognizable soccer rules or completely inappropriate for the age group</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>- The animation shows players using their hands to touch the ball, which contradicts the basic rules of soccer.
+- The characters are not colorful or kid-friendly, making the animation less engaging for young children.
+- The soccer field is depicted incorrectly, such as having no goals or an unrealistic size.
+- The explanation of the rules is too complex for young children to understand.</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>073_veo31_EVB-Art-ELow-S-UC-1-095.mp4</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>073_sora2_EVB-Art-ELow-S-UC-1-095.mp4</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>073_kling3_EVB-Art-ELow-S-UC-1-095.mp4</t>
         </is>
       </c>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="13" t="inlineStr">
         <is>
           <t>073_wan22_EVB-Art-ELow-S-UC-1-095.mp4</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="14" t="inlineStr">
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>073_wan26_EVB-Art-ELow-S-UC-1-095.mp4</t>
         </is>
       </c>
-      <c r="V6" s="10" t="inlineStr"/>
-      <c r="W6" s="8" t="inlineStr"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="8" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1099,7 +1159,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1110,46 +1170,60 @@
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Answer: Optimal shot put angle is slightly less than 45 degrees when release height is above ground, derived from projectile motion equations
-Key visuals: shot put athlete, projectile trajectory, equation display, angle diagram, release height factor
-Rubric: 9-10: Complete derivation with correct equations, clear visualization of projectile path, accurate conclusion about optimal angle less than 45 degrees due to release height, all steps logically connected. 7-8: Mostly correct derivation with minor gaps, projectile visualization present, correct final answer. 5-6: Basic projectile concepts shown but incomplete derivation, some equations present but logical connection weak. 3-4: Attempt at physics content but significant errors in equations or wrong conclusion. 1-2: No recognizable physics content or completely incorrect analysis.</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr">
+Key visuals: shot put athlete, projectile trajectory, equation display, angle diagram, release height factor</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Complete derivation with correct equations, clear visualization of projectile path, accurate conclusion about optimal angle less than 45 degrees due to release height, all steps logically connected
+- 4: Mostly correct derivation with minor gaps, projectile visualization present, correct final answer
+- 3: Basic projectile concepts shown but incomplete derivation, some equations present but logical connection weak
+- 2: Attempt at physics content but significant errors in equations or wrong conclusion
+- 1: No recognizable physics content or completely incorrect analysis</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>- Incorrectly depicting the projectile trajectory as a straight line instead of a parabolic curve.
+- Failing to show the initial velocity and mass of the shot put athlete.
+- Misrepresenting the optimal launch angle as exactly 45 degrees instead of slightly less due to the release height.</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>074_veo31_EVB-Art-Col-S-UC-5-096.mp4</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>074_sora2_EVB-Art-Col-S-UC-5-096.mp4</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>074_kling3_EVB-Art-Col-S-UC-5-096.mp4</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>074_wan22_EVB-Art-Col-S-UC-5-096.mp4</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr"/>
-      <c r="U7" s="14" t="inlineStr">
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>074_wan26_EVB-Art-Col-S-UC-5-096.mp4</t>
         </is>
       </c>
-      <c r="V7" s="10" t="inlineStr"/>
-      <c r="W7" s="8" t="inlineStr"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="8" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1174,7 +1248,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1185,54 +1259,68 @@
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Misconception: Static stretching before exercise prevents all injuries
-Correct: Pre-exercise static stretching does not prevent all injuries and may even reduce performance; dynamic warm-ups are more effective for injury prevention, though no method eliminates all injury risk
-Rubric: 9-10: The video accurately addresses the misconception, distinguishing between static and dynamic stretching, presenting evidence that static stretching alone does not prevent all injuries, and recommending dynamic warm-ups. 7-8: The video mostly corrects the misconception, mentioning that stretching has limitations in injury prevention, with minor omissions. 5-6: The video presents stretching as beneficial but acknowledges some limitations, without clearly correcting the misconception. 3-4: The video largely reinforces the misconception that stretching prevents all injuries, with minimal nuance. 1-2: The video fully promotes the misconception without any correction or nuance.</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
+Correct: Pre-exercise static stretching does not prevent all injuries and may even reduce performance; dynamic warm-ups are more effective for injury prevention, though no method eliminates all injury risk</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>- 5: The video accurately addresses the misconception, distinguishing between static and dynamic stretching, presenting evidence that static stretching alone does not prevent all injuries, and recommending dynamic warm-ups
+- 4: The video mostly corrects the misconception, mentioning that stretching has limitations in injury prevention, with minor omissions
+- 3: The video presents stretching as beneficial but acknowledges some limitations, without clearly correcting the misconception
+- 2: The video largely reinforces the misconception that stretching prevents all injuries, with minimal nuance
+- 1: The video fully promotes the misconception without any correction or nuance</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>- The video shows a person performing static stretching and claims it prevents all injuries without mentioning dynamic warm-ups.
+- The video inaccurately depicts static stretching as the sole method for injury prevention, ignoring other factors like proper technique and conditioning.
+- The video includes outdated or incorrect statistics that suggest static stretching is effective for all types of injuries.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>044_veo31_EVB-Art-None-A-ES-1-093.mp4</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>044_sora2_EVB-Art-None-A-ES-1-093.mp4</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>044_kling3_EVB-Art-None-A-ES-1-093.mp4</t>
         </is>
       </c>
-      <c r="P8" s="10" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="13" t="inlineStr">
         <is>
           <t>044_wan22_EVB-Art-None-A-ES-1-093.mp4</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr"/>
-      <c r="U8" s="14" t="inlineStr">
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>044_wan26_EVB-Art-None-A-ES-1-093.mp4</t>
         </is>
       </c>
-      <c r="V8" s="10" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="8" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="J2 J3 M2 M3 P2 P3 S2 S3 V2 V3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid score" error="Enter 0, 0.5, or 1" promptTitle="exact_match" prompt="0=Wrong, 0.5=Partial, 1=Correct" type="list">
+    <dataValidation sqref="K2 K3 N2 N3 Q2 Q3 T2 T3 W2 W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="0, 0.5, 1 중 하나를 입력하세요" type="list">
       <formula1>"0,0.5,1"</formula1>
     </dataValidation>
-    <dataValidation sqref="J4 J5 J6 J7 J8 M4 M5 M6 M7 M8 P4 P5 P6 P7 P8 S4 S5 S6 S7 S8 V4 V5 V6 V7 V8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid score" error="Enter a number between 1 and 10" promptTitle="rubric_10pt" prompt="1-2: Very Poor, 3-4: Poor, 5-6: Adequate, 7-8: Good, 9-10: Excellent" type="list">
-      <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
+    <dataValidation sqref="K4 K5 K6 K7 K8 N4 N5 N6 N7 N8 Q4 Q5 Q6 Q7 Q8 T4 T5 T6 T7 T8 W4 W5 W6 W7 W8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="1~5 사이의 정수를 입력하세요" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
